--- a/docs/Расчёты.xlsx
+++ b/docs/Расчёты.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\rsschool\react-performance\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B257B00-8D0B-4B30-8C09-F8BE79356736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529D0642-A9F5-423E-B68E-24D5BFC6B42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1875" yWindow="2445" windowWidth="16200" windowHeight="9307" xr2:uid="{7A107E4D-BF9D-45CD-9CCA-4EA53CC16E3F}"/>
   </bookViews>
@@ -22,10 +22,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -388,11 +384,11 @@
         <v>96</v>
       </c>
       <c r="B1" s="1">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1">
         <f>(A1-B1)/A1*100</f>
-        <v>48.958333333333329</v>
+        <v>94.791666666666657</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -438,11 +434,11 @@
       </c>
       <c r="B5" s="1">
         <f>AVERAGE(B1:B4)</f>
-        <v>22.274999999999999</v>
+        <v>11.275</v>
       </c>
       <c r="C5" s="1">
         <f>AVERAGE(C1:C4)</f>
-        <v>76.873206013174496</v>
+        <v>88.331539346507824</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Расчёты.xlsx
+++ b/docs/Расчёты.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\rsschool\react-performance\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529D0642-A9F5-423E-B68E-24D5BFC6B42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB4FD22A-2CFC-47FF-8EC5-6F98523DF67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1875" yWindow="2445" windowWidth="16200" windowHeight="9307" xr2:uid="{7A107E4D-BF9D-45CD-9CCA-4EA53CC16E3F}"/>
   </bookViews>
@@ -22,6 +22,14 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>United</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -373,13 +381,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{870D54C0-71E7-4CB8-9B50-FC03F9B60124}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
         <v>96</v>
       </c>
@@ -391,7 +399,7 @@
         <v>94.791666666666657</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>13</v>
       </c>
@@ -402,43 +410,46 @@
         <f t="shared" ref="C2:C4" si="0">(A2-B2)/A2*100</f>
         <v>99.230769230769226</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>98</v>
       </c>
       <c r="B3" s="1">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <f t="shared" si="0"/>
-        <v>62.244897959183675</v>
+        <v>89.795918367346943</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>102</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="0"/>
-        <v>97.058823529411768</v>
+        <v>98.039215686274503</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <f>AVERAGE(A1:A4)</f>
         <v>77.25</v>
       </c>
       <c r="B5" s="1">
         <f>AVERAGE(B1:B4)</f>
-        <v>11.275</v>
+        <v>4.2750000000000004</v>
       </c>
       <c r="C5" s="1">
         <f>AVERAGE(C1:C4)</f>
-        <v>88.331539346507824</v>
+        <v>95.464392487764343</v>
       </c>
     </row>
   </sheetData>
